--- a/00_specifications/ADaM_spec.xlsx
+++ b/00_specifications/ADaM_spec.xlsx
@@ -1,49 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Study" sheetId="1" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
-    <sheet name="Variables" sheetId="3" r:id="rId3"/>
-    <sheet name="ValueLevel" sheetId="4" r:id="rId4"/>
-    <sheet name="WhereClauses" sheetId="5" r:id="rId5"/>
-    <sheet name="Codelists" sheetId="6" r:id="rId6"/>
-    <sheet name="Dictionaries" sheetId="7" r:id="rId7"/>
-    <sheet name="Methods" sheetId="8" r:id="rId8"/>
-    <sheet name="Comments" sheetId="9" r:id="rId9"/>
-    <sheet name="Documents" sheetId="10" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Study" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValueLevel" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WhereClauses" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codelists" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionaries" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methods" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comments" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -62,16 +63,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -359,11 +427,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Attribute</t>
@@ -453,11 +525,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -480,11 +556,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -796,11 +876,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P158"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Order</t>
@@ -883,7 +967,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -906,7 +990,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>40</v>
       </c>
       <c r="I2" t="inlineStr">
@@ -921,7 +1005,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -944,7 +1028,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>40</v>
       </c>
       <c r="I3" t="inlineStr">
@@ -959,7 +1043,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -982,7 +1066,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>20</v>
       </c>
       <c r="I4" t="inlineStr">
@@ -997,7 +1081,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1020,7 +1104,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="I5" t="inlineStr">
@@ -1035,7 +1119,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1058,7 +1142,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>8</v>
       </c>
       <c r="I6" t="inlineStr">
@@ -1073,7 +1157,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1096,7 +1180,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="I7" t="inlineStr">
@@ -1116,7 +1200,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1139,7 +1223,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>8</v>
       </c>
       <c r="I8" t="inlineStr">
@@ -1154,7 +1238,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1177,7 +1261,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>40</v>
       </c>
       <c r="I9" t="inlineStr">
@@ -1192,7 +1276,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1215,7 +1299,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>40</v>
       </c>
       <c r="I10" t="inlineStr">
@@ -1230,7 +1314,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1253,7 +1337,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
@@ -1273,7 +1357,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,7 +1380,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>40</v>
       </c>
       <c r="I12" t="inlineStr">
@@ -1316,7 +1400,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1339,7 +1423,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
       <c r="I13" t="inlineStr">
@@ -1359,7 +1443,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1382,7 +1466,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>40</v>
       </c>
       <c r="I14" t="inlineStr">
@@ -1402,7 +1486,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1425,7 +1509,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>8</v>
       </c>
       <c r="I15" t="inlineStr">
@@ -1445,7 +1529,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1468,7 +1552,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="I16" t="inlineStr">
@@ -1483,7 +1567,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1506,7 +1590,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="I17" t="inlineStr">
@@ -1526,7 +1610,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1549,7 +1633,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="I18" t="inlineStr">
@@ -1569,7 +1653,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1592,7 +1676,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>8</v>
       </c>
       <c r="I19" t="inlineStr">
@@ -1612,7 +1696,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1635,7 +1719,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
@@ -1660,7 +1744,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,7 +1767,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
@@ -1708,7 +1792,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1731,7 +1815,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
@@ -1751,7 +1835,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1774,7 +1858,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
@@ -1794,7 +1878,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1817,7 +1901,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>10</v>
       </c>
       <c r="I24" t="inlineStr">
@@ -1832,7 +1916,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1855,7 +1939,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>200</v>
       </c>
       <c r="I25" t="inlineStr">
@@ -1870,7 +1954,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1893,7 +1977,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>10</v>
       </c>
       <c r="I26" t="inlineStr">
@@ -1908,7 +1992,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1931,7 +2015,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>8</v>
       </c>
       <c r="I27" t="inlineStr">
@@ -1951,7 +2035,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1974,7 +2058,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
@@ -1999,7 +2083,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2022,7 +2106,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
@@ -2042,7 +2126,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2065,7 +2149,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
@@ -2090,7 +2174,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2113,7 +2197,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>8</v>
       </c>
       <c r="I31" t="inlineStr">
@@ -2128,7 +2212,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2151,7 +2235,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="I32" t="inlineStr">
@@ -2166,7 +2250,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2189,7 +2273,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>8</v>
       </c>
       <c r="I33" t="inlineStr">
@@ -2204,7 +2288,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2227,7 +2311,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>8</v>
       </c>
       <c r="I34" t="inlineStr">
@@ -2242,7 +2326,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2265,7 +2349,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>8</v>
       </c>
       <c r="I35" t="inlineStr">
@@ -2280,7 +2364,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2303,7 +2387,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>20</v>
       </c>
       <c r="I36" t="inlineStr">
@@ -2318,7 +2402,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2341,7 +2425,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
@@ -2361,7 +2445,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2384,7 +2468,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
@@ -2404,7 +2488,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2427,7 +2511,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
@@ -2447,7 +2531,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2470,7 +2554,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
@@ -2490,7 +2574,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2513,7 +2597,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
@@ -2533,7 +2617,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2556,7 +2640,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
@@ -2576,7 +2660,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2599,7 +2683,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="I43" t="inlineStr">
@@ -2619,7 +2703,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44">
+      <c r="A44" t="n">
         <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2642,7 +2726,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="F44" t="n">
         <v>40</v>
       </c>
       <c r="I44" t="inlineStr">
@@ -2657,7 +2741,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45">
+      <c r="A45" t="n">
         <v>2</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2680,7 +2764,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="F45" t="n">
         <v>40</v>
       </c>
       <c r="I45" t="inlineStr">
@@ -2695,7 +2779,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46">
+      <c r="A46" t="n">
         <v>3</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2718,7 +2802,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="F46" t="n">
         <v>20</v>
       </c>
       <c r="I46" t="inlineStr">
@@ -2733,7 +2817,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47">
+      <c r="A47" t="n">
         <v>4</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2756,7 +2840,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="F47" t="n">
         <v>40</v>
       </c>
       <c r="I47" t="inlineStr">
@@ -2776,7 +2860,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48">
+      <c r="A48" t="n">
         <v>5</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2799,7 +2883,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="F48" t="n">
         <v>8</v>
       </c>
       <c r="I48" t="inlineStr">
@@ -2819,7 +2903,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49">
+      <c r="A49" t="n">
         <v>6</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2842,7 +2926,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="F49" t="n">
         <v>10</v>
       </c>
       <c r="I49" t="inlineStr">
@@ -2857,7 +2941,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50">
+      <c r="A50" t="n">
         <v>7</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2880,7 +2964,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="F50" t="n">
         <v>20</v>
       </c>
       <c r="I50" t="inlineStr">
@@ -2900,7 +2984,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51">
+      <c r="A51" t="n">
         <v>8</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2923,7 +3007,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="F51" t="n">
         <v>200</v>
       </c>
       <c r="I51" t="inlineStr">
@@ -2938,7 +3022,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52">
+      <c r="A52" t="n">
         <v>9</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2961,7 +3045,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="F52" t="n">
         <v>20</v>
       </c>
       <c r="I52" t="inlineStr">
@@ -2976,7 +3060,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53">
+      <c r="A53" t="n">
         <v>10</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2999,7 +3083,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="F53" t="n">
         <v>8</v>
       </c>
       <c r="I53" t="inlineStr">
@@ -3014,7 +3098,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54">
+      <c r="A54" t="n">
         <v>11</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3037,7 +3121,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="F54" t="n">
         <v>100</v>
       </c>
       <c r="I54" t="inlineStr">
@@ -3052,7 +3136,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55">
+      <c r="A55" t="n">
         <v>12</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3075,7 +3159,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="F55" t="n">
         <v>40</v>
       </c>
       <c r="I55" t="inlineStr">
@@ -3090,7 +3174,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56">
+      <c r="A56" t="n">
         <v>1</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3113,7 +3197,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="F56" t="n">
         <v>40</v>
       </c>
       <c r="I56" t="inlineStr">
@@ -3128,7 +3212,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57">
+      <c r="A57" t="n">
         <v>2</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3151,7 +3235,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="F57" t="n">
         <v>40</v>
       </c>
       <c r="I57" t="inlineStr">
@@ -3166,7 +3250,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58">
+      <c r="A58" t="n">
         <v>3</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3189,7 +3273,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="F58" t="n">
         <v>100</v>
       </c>
       <c r="I58" t="inlineStr">
@@ -3204,7 +3288,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59">
+      <c r="A59" t="n">
         <v>4</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3227,7 +3311,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="F59" t="n">
         <v>100</v>
       </c>
       <c r="I59" t="inlineStr">
@@ -3242,7 +3326,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60">
+      <c r="A60" t="n">
         <v>5</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3265,7 +3349,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="F60" t="n">
         <v>200</v>
       </c>
       <c r="I60" t="inlineStr">
@@ -3280,7 +3364,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61">
+      <c r="A61" t="n">
         <v>6</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3303,7 +3387,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="F61" t="n">
         <v>10</v>
       </c>
       <c r="I61" t="inlineStr">
@@ -3318,7 +3402,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62">
+      <c r="A62" t="n">
         <v>7</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3341,7 +3425,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="F62" t="n">
         <v>10</v>
       </c>
       <c r="I62" t="inlineStr">
@@ -3356,7 +3440,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63">
+      <c r="A63" t="n">
         <v>8</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3379,7 +3463,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="F63" t="n">
         <v>200</v>
       </c>
       <c r="I63" t="inlineStr">
@@ -3394,7 +3478,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64">
+      <c r="A64" t="n">
         <v>9</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3417,7 +3501,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="F64" t="n">
         <v>8</v>
       </c>
       <c r="I64" t="inlineStr">
@@ -3432,7 +3516,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65">
+      <c r="A65" t="n">
         <v>10</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3455,7 +3539,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
@@ -3475,7 +3559,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66">
+      <c r="A66" t="n">
         <v>11</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -3498,7 +3582,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="I66" t="inlineStr">
@@ -3518,7 +3602,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67">
+      <c r="A67" t="n">
         <v>12</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -3541,7 +3625,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="I67" t="inlineStr">
@@ -3561,7 +3645,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68">
+      <c r="A68" t="n">
         <v>13</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -3584,7 +3668,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="F68" t="n">
         <v>10</v>
       </c>
       <c r="I68" t="inlineStr">
@@ -3599,7 +3683,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69">
+      <c r="A69" t="n">
         <v>14</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -3622,7 +3706,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="I69" t="inlineStr">
@@ -3642,7 +3726,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70">
+      <c r="A70" t="n">
         <v>15</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -3665,7 +3749,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="I70" t="inlineStr">
@@ -3685,7 +3769,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71">
+      <c r="A71" t="n">
         <v>1</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -3708,7 +3792,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="F71" t="n">
         <v>40</v>
       </c>
       <c r="I71" t="inlineStr">
@@ -3723,7 +3807,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72">
+      <c r="A72" t="n">
         <v>2</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -3746,7 +3830,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="F72" t="n">
         <v>40</v>
       </c>
       <c r="I72" t="inlineStr">
@@ -3761,7 +3845,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73">
+      <c r="A73" t="n">
         <v>3</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -3784,7 +3868,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="F73" t="n">
         <v>100</v>
       </c>
       <c r="I73" t="inlineStr">
@@ -3799,7 +3883,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74">
+      <c r="A74" t="n">
         <v>4</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -3822,7 +3906,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="F74" t="n">
         <v>100</v>
       </c>
       <c r="I74" t="inlineStr">
@@ -3837,7 +3921,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75">
+      <c r="A75" t="n">
         <v>5</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -3860,7 +3944,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="F75" t="n">
         <v>100</v>
       </c>
       <c r="I75" t="inlineStr">
@@ -3875,7 +3959,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76">
+      <c r="A76" t="n">
         <v>6</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -3898,7 +3982,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="F76" t="n">
         <v>10</v>
       </c>
       <c r="I76" t="inlineStr">
@@ -3913,7 +3997,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77">
+      <c r="A77" t="n">
         <v>7</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -3936,7 +4020,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="F77" t="n">
         <v>8</v>
       </c>
       <c r="I77" t="inlineStr">
@@ -3951,7 +4035,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78">
+      <c r="A78" t="n">
         <v>8</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3974,7 +4058,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
@@ -3994,7 +4078,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79">
+      <c r="A79" t="n">
         <v>9</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -4017,7 +4101,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="F79" t="n">
         <v>40</v>
       </c>
       <c r="I79" t="inlineStr">
@@ -4032,7 +4116,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80">
+      <c r="A80" t="n">
         <v>10</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -4055,7 +4139,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="F80" t="n">
         <v>10</v>
       </c>
       <c r="I80" t="inlineStr">
@@ -4070,7 +4154,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81">
+      <c r="A81" t="n">
         <v>11</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -4093,7 +4177,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="F81" t="n">
         <v>10</v>
       </c>
       <c r="I81" t="inlineStr">
@@ -4108,7 +4192,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82">
+      <c r="A82" t="n">
         <v>12</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -4131,7 +4215,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="F82" t="n">
         <v>8</v>
       </c>
       <c r="I82" t="inlineStr">
@@ -4146,7 +4230,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83">
+      <c r="A83" t="n">
         <v>13</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -4169,7 +4253,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="F83" t="n">
         <v>8</v>
       </c>
       <c r="I83" t="inlineStr">
@@ -4184,7 +4268,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84">
+      <c r="A84" t="n">
         <v>14</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -4207,7 +4291,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="F84" t="n">
         <v>100</v>
       </c>
       <c r="I84" t="inlineStr">
@@ -4222,7 +4306,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85">
+      <c r="A85" t="n">
         <v>15</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -4245,7 +4329,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="F85" t="n">
         <v>100</v>
       </c>
       <c r="I85" t="inlineStr">
@@ -4260,7 +4344,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86">
+      <c r="A86" t="n">
         <v>16</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -4283,7 +4367,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="F86" t="n">
         <v>100</v>
       </c>
       <c r="I86" t="inlineStr">
@@ -4298,7 +4382,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87">
+      <c r="A87" t="n">
         <v>17</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -4321,7 +4405,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="F87" t="n">
         <v>8</v>
       </c>
       <c r="I87" t="inlineStr">
@@ -4336,7 +4420,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88">
+      <c r="A88" t="n">
         <v>18</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -4359,7 +4443,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="F88" t="n">
         <v>10</v>
       </c>
       <c r="I88" t="inlineStr">
@@ -4374,7 +4458,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89">
+      <c r="A89" t="n">
         <v>19</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -4397,7 +4481,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="F89" t="n">
         <v>8</v>
       </c>
       <c r="I89" t="inlineStr">
@@ -4412,7 +4496,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90">
+      <c r="A90" t="n">
         <v>20</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -4435,7 +4519,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="F90" t="n">
         <v>10</v>
       </c>
       <c r="I90" t="inlineStr">
@@ -4450,7 +4534,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91">
+      <c r="A91" t="n">
         <v>21</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -4473,7 +4557,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="F91" t="n">
         <v>10</v>
       </c>
       <c r="I91" t="inlineStr">
@@ -4488,7 +4572,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92">
+      <c r="A92" t="n">
         <v>22</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -4511,7 +4595,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="F92" t="n">
         <v>8</v>
       </c>
       <c r="I92" t="inlineStr">
@@ -4526,7 +4610,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93">
+      <c r="A93" t="n">
         <v>23</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -4549,7 +4633,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="I93" t="inlineStr">
@@ -4569,7 +4653,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94">
+      <c r="A94" t="n">
         <v>24</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -4592,7 +4676,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="I94" t="inlineStr">
@@ -4612,7 +4696,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95">
+      <c r="A95" t="n">
         <v>25</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -4635,7 +4719,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="F95" t="n">
         <v>8</v>
       </c>
       <c r="I95" t="inlineStr">
@@ -4650,7 +4734,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96">
+      <c r="A96" t="n">
         <v>26</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -4673,7 +4757,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="F96" t="n">
         <v>20</v>
       </c>
       <c r="I96" t="inlineStr">
@@ -4688,7 +4772,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97">
+      <c r="A97" t="n">
         <v>27</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -4711,7 +4795,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="F97" t="n">
         <v>8</v>
       </c>
       <c r="I97" t="inlineStr">
@@ -4726,7 +4810,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98">
+      <c r="A98" t="n">
         <v>28</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -4749,7 +4833,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="F98" t="n">
         <v>20</v>
       </c>
       <c r="I98" t="inlineStr">
@@ -4769,7 +4853,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99">
+      <c r="A99" t="n">
         <v>29</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -4792,7 +4876,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="F99" t="n">
         <v>8</v>
       </c>
       <c r="I99" t="inlineStr">
@@ -4812,7 +4896,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100">
+      <c r="A100" t="n">
         <v>1</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -4835,7 +4919,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="F100" t="n">
         <v>40</v>
       </c>
       <c r="I100" t="inlineStr">
@@ -4850,7 +4934,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101">
+      <c r="A101" t="n">
         <v>2</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -4873,7 +4957,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="F101" t="n">
         <v>40</v>
       </c>
       <c r="I101" t="inlineStr">
@@ -4888,7 +4972,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102">
+      <c r="A102" t="n">
         <v>3</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -4911,7 +4995,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="F102" t="n">
         <v>20</v>
       </c>
       <c r="I102" t="inlineStr">
@@ -4926,7 +5010,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103">
+      <c r="A103" t="n">
         <v>4</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -4949,7 +5033,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="F103" t="n">
         <v>40</v>
       </c>
       <c r="I103" t="inlineStr">
@@ -4969,7 +5053,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104">
+      <c r="A104" t="n">
         <v>5</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -4992,7 +5076,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="F104" t="n">
         <v>10</v>
       </c>
       <c r="I104" t="inlineStr">
@@ -5007,7 +5091,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105">
+      <c r="A105" t="n">
         <v>6</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -5030,7 +5114,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="F105" t="n">
         <v>20</v>
       </c>
       <c r="I105" t="inlineStr">
@@ -5050,7 +5134,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106">
+      <c r="A106" t="n">
         <v>7</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -5073,7 +5157,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="F106" t="n">
         <v>200</v>
       </c>
       <c r="I106" t="inlineStr">
@@ -5088,7 +5172,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107">
+      <c r="A107" t="n">
         <v>8</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -5111,7 +5195,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F107">
+      <c r="F107" t="n">
         <v>8</v>
       </c>
       <c r="I107" t="inlineStr">
@@ -5126,7 +5210,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108">
+      <c r="A108" t="n">
         <v>9</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -5149,7 +5233,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F108">
+      <c r="F108" t="n">
         <v>20</v>
       </c>
       <c r="I108" t="inlineStr">
@@ -5164,7 +5248,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109">
+      <c r="A109" t="n">
         <v>10</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -5187,7 +5271,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F109">
+      <c r="F109" t="n">
         <v>8</v>
       </c>
       <c r="I109" t="inlineStr">
@@ -5202,7 +5286,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110">
+      <c r="A110" t="n">
         <v>11</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -5225,7 +5309,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F110">
+      <c r="F110" t="n">
         <v>100</v>
       </c>
       <c r="I110" t="inlineStr">
@@ -5240,7 +5324,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111">
+      <c r="A111" t="n">
         <v>12</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -5263,7 +5347,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F111">
+      <c r="F111" t="n">
         <v>100</v>
       </c>
       <c r="I111" t="inlineStr">
@@ -5278,7 +5362,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112">
+      <c r="A112" t="n">
         <v>13</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -5301,7 +5385,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F112">
+      <c r="F112" t="n">
         <v>100</v>
       </c>
       <c r="I112" t="inlineStr">
@@ -5316,7 +5400,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113">
+      <c r="A113" t="n">
         <v>14</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -5339,7 +5423,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F113">
+      <c r="F113" t="n">
         <v>20</v>
       </c>
       <c r="I113" t="inlineStr">
@@ -5354,7 +5438,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114">
+      <c r="A114" t="n">
         <v>15</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -5377,7 +5461,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F114">
+      <c r="F114" t="n">
         <v>40</v>
       </c>
       <c r="I114" t="inlineStr">
@@ -5392,7 +5476,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115">
+      <c r="A115" t="n">
         <v>16</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -5415,7 +5499,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F115">
+      <c r="F115" t="n">
         <v>8</v>
       </c>
       <c r="I115" t="inlineStr">
@@ -5430,7 +5514,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116">
+      <c r="A116" t="n">
         <v>17</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -5453,7 +5537,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="F116" t="n">
         <v>8</v>
       </c>
       <c r="I116" t="inlineStr">
@@ -5468,7 +5552,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117">
+      <c r="A117" t="n">
         <v>18</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -5491,7 +5575,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F117">
+      <c r="F117" t="n">
         <v>8</v>
       </c>
       <c r="I117" t="inlineStr">
@@ -5506,7 +5590,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118">
+      <c r="A118" t="n">
         <v>19</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -5529,7 +5613,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F118">
+      <c r="F118" t="n">
         <v>8</v>
       </c>
       <c r="I118" t="inlineStr">
@@ -5544,7 +5628,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119">
+      <c r="A119" t="n">
         <v>20</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -5567,7 +5651,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F119">
+      <c r="F119" t="n">
         <v>100</v>
       </c>
       <c r="I119" t="inlineStr">
@@ -5582,7 +5666,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120">
+      <c r="A120" t="n">
         <v>21</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -5605,7 +5689,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F120">
+      <c r="F120" t="n">
         <v>8</v>
       </c>
       <c r="I120" t="inlineStr">
@@ -5620,7 +5704,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121">
+      <c r="A121" t="n">
         <v>22</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -5643,7 +5727,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F121">
+      <c r="F121" t="n">
         <v>8</v>
       </c>
       <c r="I121" t="inlineStr">
@@ -5658,7 +5742,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122">
+      <c r="A122" t="n">
         <v>23</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -5681,7 +5765,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F122">
+      <c r="F122" t="n">
         <v>8</v>
       </c>
       <c r="I122" t="inlineStr">
@@ -5696,7 +5780,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123">
+      <c r="A123" t="n">
         <v>24</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -5719,7 +5803,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F123">
+      <c r="F123" t="n">
         <v>1</v>
       </c>
       <c r="I123" t="inlineStr">
@@ -5739,7 +5823,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124">
+      <c r="A124" t="n">
         <v>25</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -5762,7 +5846,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F124">
+      <c r="F124" t="n">
         <v>1</v>
       </c>
       <c r="I124" t="inlineStr">
@@ -5782,7 +5866,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125">
+      <c r="A125" t="n">
         <v>26</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -5805,7 +5889,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F125">
+      <c r="F125" t="n">
         <v>8</v>
       </c>
       <c r="I125" t="inlineStr">
@@ -5820,7 +5904,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126">
+      <c r="A126" t="n">
         <v>27</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -5843,7 +5927,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F126">
+      <c r="F126" t="n">
         <v>10</v>
       </c>
       <c r="I126" t="inlineStr">
@@ -5858,7 +5942,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127">
+      <c r="A127" t="n">
         <v>1</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -5881,7 +5965,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F127">
+      <c r="F127" t="n">
         <v>40</v>
       </c>
       <c r="I127" t="inlineStr">
@@ -5896,7 +5980,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128">
+      <c r="A128" t="n">
         <v>2</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -5919,7 +6003,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F128">
+      <c r="F128" t="n">
         <v>40</v>
       </c>
       <c r="I128" t="inlineStr">
@@ -5934,7 +6018,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129">
+      <c r="A129" t="n">
         <v>3</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -5957,7 +6041,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F129">
+      <c r="F129" t="n">
         <v>20</v>
       </c>
       <c r="I129" t="inlineStr">
@@ -5972,7 +6056,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130">
+      <c r="A130" t="n">
         <v>4</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -5995,7 +6079,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F130">
+      <c r="F130" t="n">
         <v>40</v>
       </c>
       <c r="I130" t="inlineStr">
@@ -6015,7 +6099,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131">
+      <c r="A131" t="n">
         <v>5</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -6038,7 +6122,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F131">
+      <c r="F131" t="n">
         <v>10</v>
       </c>
       <c r="I131" t="inlineStr">
@@ -6053,7 +6137,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132">
+      <c r="A132" t="n">
         <v>6</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -6076,7 +6160,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F132">
+      <c r="F132" t="n">
         <v>20</v>
       </c>
       <c r="I132" t="inlineStr">
@@ -6096,7 +6180,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133">
+      <c r="A133" t="n">
         <v>7</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -6119,7 +6203,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F133">
+      <c r="F133" t="n">
         <v>200</v>
       </c>
       <c r="I133" t="inlineStr">
@@ -6134,7 +6218,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134">
+      <c r="A134" t="n">
         <v>8</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -6157,7 +6241,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F134">
+      <c r="F134" t="n">
         <v>100</v>
       </c>
       <c r="I134" t="inlineStr">
@@ -6172,7 +6256,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135">
+      <c r="A135" t="n">
         <v>9</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -6195,7 +6279,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F135">
+      <c r="F135" t="n">
         <v>10</v>
       </c>
       <c r="I135" t="inlineStr">
@@ -6210,7 +6294,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136">
+      <c r="A136" t="n">
         <v>10</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -6233,7 +6317,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F136">
+      <c r="F136" t="n">
         <v>8</v>
       </c>
       <c r="I136" t="inlineStr">
@@ -6248,7 +6332,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137">
+      <c r="A137" t="n">
         <v>11</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -6271,7 +6355,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F137">
+      <c r="F137" t="n">
         <v>40</v>
       </c>
       <c r="I137" t="inlineStr">
@@ -6286,7 +6370,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138">
+      <c r="A138" t="n">
         <v>12</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -6309,7 +6393,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F138">
+      <c r="F138" t="n">
         <v>1</v>
       </c>
       <c r="I138" t="inlineStr">
@@ -6329,7 +6413,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139">
+      <c r="A139" t="n">
         <v>13</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -6352,7 +6436,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F139">
+      <c r="F139" t="n">
         <v>8</v>
       </c>
       <c r="I139" t="inlineStr">
@@ -6367,7 +6451,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140">
+      <c r="A140" t="n">
         <v>1</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -6390,7 +6474,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F140">
+      <c r="F140" t="n">
         <v>40</v>
       </c>
       <c r="I140" t="inlineStr">
@@ -6405,7 +6489,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141">
+      <c r="A141" t="n">
         <v>2</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -6428,7 +6512,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F141">
+      <c r="F141" t="n">
         <v>40</v>
       </c>
       <c r="I141" t="inlineStr">
@@ -6443,7 +6527,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142">
+      <c r="A142" t="n">
         <v>3</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -6466,7 +6550,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F142">
+      <c r="F142" t="n">
         <v>20</v>
       </c>
       <c r="I142" t="inlineStr">
@@ -6481,7 +6565,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143">
+      <c r="A143" t="n">
         <v>4</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -6504,7 +6588,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F143">
+      <c r="F143" t="n">
         <v>10</v>
       </c>
       <c r="I143" t="inlineStr">
@@ -6519,7 +6603,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144">
+      <c r="A144" t="n">
         <v>5</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -6542,7 +6626,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F144">
+      <c r="F144" t="n">
         <v>40</v>
       </c>
       <c r="I144" t="inlineStr">
@@ -6562,7 +6646,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145">
+      <c r="A145" t="n">
         <v>6</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -6585,7 +6669,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F145">
+      <c r="F145" t="n">
         <v>8</v>
       </c>
       <c r="I145" t="inlineStr">
@@ -6605,7 +6689,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146">
+      <c r="A146" t="n">
         <v>7</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -6628,7 +6712,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F146">
+      <c r="F146" t="n">
         <v>1</v>
       </c>
       <c r="I146" t="inlineStr">
@@ -6648,7 +6732,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147">
+      <c r="A147" t="n">
         <v>8</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -6671,7 +6755,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F147">
+      <c r="F147" t="n">
         <v>1</v>
       </c>
       <c r="I147" t="inlineStr">
@@ -6691,7 +6775,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148">
+      <c r="A148" t="n">
         <v>9</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -6714,7 +6798,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F148">
+      <c r="F148" t="n">
         <v>20</v>
       </c>
       <c r="I148" t="inlineStr">
@@ -6734,7 +6818,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149">
+      <c r="A149" t="n">
         <v>10</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -6757,7 +6841,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F149">
+      <c r="F149" t="n">
         <v>200</v>
       </c>
       <c r="I149" t="inlineStr">
@@ -6772,7 +6856,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150">
+      <c r="A150" t="n">
         <v>11</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -6795,7 +6879,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F150">
+      <c r="F150" t="n">
         <v>8</v>
       </c>
       <c r="I150" t="inlineStr">
@@ -6810,7 +6894,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151">
+      <c r="A151" t="n">
         <v>12</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -6833,7 +6917,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F151">
+      <c r="F151" t="n">
         <v>20</v>
       </c>
       <c r="I151" t="inlineStr">
@@ -6848,7 +6932,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152">
+      <c r="A152" t="n">
         <v>13</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -6871,7 +6955,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F152">
+      <c r="F152" t="n">
         <v>10</v>
       </c>
       <c r="I152" t="inlineStr">
@@ -6886,7 +6970,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153">
+      <c r="A153" t="n">
         <v>14</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -6909,7 +6993,7 @@
           <t>date</t>
         </is>
       </c>
-      <c r="F153">
+      <c r="F153" t="n">
         <v>10</v>
       </c>
       <c r="I153" t="inlineStr">
@@ -6924,7 +7008,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154">
+      <c r="A154" t="n">
         <v>15</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -6947,7 +7031,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F154">
+      <c r="F154" t="n">
         <v>8</v>
       </c>
       <c r="I154" t="inlineStr">
@@ -6972,7 +7056,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155">
+      <c r="A155" t="n">
         <v>16</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -6995,7 +7079,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F155">
+      <c r="F155" t="n">
         <v>100</v>
       </c>
       <c r="I155" t="inlineStr">
@@ -7010,7 +7094,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156">
+      <c r="A156" t="n">
         <v>17</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -7033,7 +7117,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F156">
+      <c r="F156" t="n">
         <v>100</v>
       </c>
       <c r="I156" t="inlineStr">
@@ -7048,7 +7132,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157">
+      <c r="A157" t="n">
         <v>18</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -7071,7 +7155,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F157">
+      <c r="F157" t="n">
         <v>8</v>
       </c>
       <c r="I157" t="inlineStr">
@@ -7091,7 +7175,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158">
+      <c r="A158" t="n">
         <v>19</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -7114,7 +7198,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F158">
+      <c r="F158" t="n">
         <v>8</v>
       </c>
       <c r="I158" t="inlineStr">
@@ -7134,11 +7218,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Order</t>
@@ -7221,7 +7309,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -7249,7 +7337,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>8</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -7264,7 +7352,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -7292,7 +7380,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>8</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -7307,7 +7395,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -7335,7 +7423,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>8</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -7350,7 +7438,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="n">
         <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -7378,7 +7466,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>8</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -7393,7 +7481,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" t="n">
         <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -7421,7 +7509,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -7436,7 +7524,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" t="n">
         <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -7464,7 +7552,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>8</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -7479,7 +7567,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="n">
         <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -7507,7 +7595,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -7527,11 +7615,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -7834,11 +7926,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H60"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -7896,7 +7992,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -7926,7 +8022,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -7956,7 +8052,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -7986,7 +8082,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -8016,7 +8112,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -8046,7 +8142,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -8076,7 +8172,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -8106,7 +8202,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -8136,7 +8232,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -8166,7 +8262,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -8196,7 +8292,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -8226,7 +8322,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -8256,7 +8352,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -8286,7 +8382,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -8316,7 +8412,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -8346,7 +8442,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -8376,7 +8472,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -8406,7 +8502,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>6</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -8436,7 +8532,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>7</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -8466,7 +8562,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -8496,7 +8592,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>9</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -8526,7 +8622,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>10</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -8556,7 +8652,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>11</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -8586,7 +8682,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>12</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -8616,7 +8712,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>13</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -8646,7 +8742,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>14</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -8676,7 +8772,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>15</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -8706,7 +8802,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>16</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -8736,7 +8832,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>17</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -8766,7 +8862,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>18</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -8796,7 +8892,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>19</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -8826,7 +8922,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>20</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -8856,7 +8952,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>21</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -8886,7 +8982,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>22</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -8916,7 +9012,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>23</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -8946,7 +9042,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>24</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -8976,7 +9072,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>25</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -9006,7 +9102,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>26</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -9036,7 +9132,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>27</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -9066,7 +9162,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>28</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -9096,7 +9192,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>29</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -9126,7 +9222,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>30</v>
       </c>
       <c r="F43" t="inlineStr">
@@ -9156,7 +9252,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>31</v>
       </c>
       <c r="F44" t="inlineStr">
@@ -9186,7 +9282,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>32</v>
       </c>
       <c r="F45" t="inlineStr">
@@ -9216,7 +9312,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>33</v>
       </c>
       <c r="F46" t="inlineStr">
@@ -9246,7 +9342,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>34</v>
       </c>
       <c r="F47" t="inlineStr">
@@ -9276,7 +9372,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>35</v>
       </c>
       <c r="F48" t="inlineStr">
@@ -9306,7 +9402,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>36</v>
       </c>
       <c r="F49" t="inlineStr">
@@ -9336,7 +9432,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>37</v>
       </c>
       <c r="F50" t="inlineStr">
@@ -9366,7 +9462,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E51">
+      <c r="E51" t="n">
         <v>38</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -9396,7 +9492,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>39</v>
       </c>
       <c r="F52" t="inlineStr">
@@ -9426,7 +9522,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E53">
+      <c r="E53" t="n">
         <v>40</v>
       </c>
       <c r="F53" t="inlineStr">
@@ -9456,7 +9552,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>41</v>
       </c>
       <c r="F54" t="inlineStr">
@@ -9486,7 +9582,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E55">
+      <c r="E55" t="n">
         <v>42</v>
       </c>
       <c r="F55" t="inlineStr">
@@ -9516,7 +9612,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E56">
+      <c r="E56" t="n">
         <v>43</v>
       </c>
       <c r="F56" t="inlineStr">
@@ -9546,7 +9642,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E57">
+      <c r="E57" t="n">
         <v>44</v>
       </c>
       <c r="F57" t="inlineStr">
@@ -9576,7 +9672,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E58">
+      <c r="E58" t="n">
         <v>45</v>
       </c>
       <c r="F58" t="inlineStr">
@@ -9606,7 +9702,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E59">
+      <c r="E59" t="n">
         <v>46</v>
       </c>
       <c r="F59" t="inlineStr">
@@ -9636,7 +9732,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E60">
+      <c r="E60" t="n">
         <v>47</v>
       </c>
       <c r="F60" t="inlineStr">
@@ -9647,6 +9743,36 @@
       <c r="H60" t="inlineStr">
         <is>
           <t>LEUKOCYTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CL.PARAMCD</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Parameter Code Codelist</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>48</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>BSGRESP</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bone Scan Progression (PCWG3)</t>
         </is>
       </c>
     </row>
@@ -9656,11 +9782,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -9693,11 +9823,15 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -10053,11 +10187,15 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>

--- a/00_specifications/ADaM_spec.xlsx
+++ b/00_specifications/ADaM_spec.xlsx
@@ -7987,6 +7987,11 @@
           <t>Yes/No Codelist</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>text</t>
@@ -8000,6 +8005,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>C49488</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8017,6 +8027,11 @@
           <t>Yes/No Codelist</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>text</t>
@@ -8030,6 +8045,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>C49487</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>No</t>
@@ -8047,6 +8067,11 @@
           <t>Sex Codelist</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>text</t>
@@ -8060,6 +8085,11 @@
           <t>M</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>C20197</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Male</t>
@@ -8077,6 +8107,11 @@
           <t>Sex Codelist</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>text</t>
@@ -8088,6 +8123,11 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>F</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>C16576</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/00_specifications/ADaM_spec.xlsx
+++ b/00_specifications/ADaM_spec.xlsx
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P158"/>
+  <dimension ref="A1:P160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" customFormat="1" s="1">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CMSTDT</t>
+          <t>ASTDT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CMENDT</t>
+          <t>AENDT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CMSTDY</t>
+          <t>ASTDY</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7207,6 +7207,82 @@
         </is>
       </c>
       <c r="K158" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>13</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ADEX</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>PARAMN</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Parameter (N)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>8</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>14</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ADEX</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AVISITN</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Analysis Visit (N)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>8</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
         <is>
           <t>Derived</t>
         </is>

--- a/00_specifications/ADaM_spec.xlsx
+++ b/00_specifications/ADaM_spec.xlsx
@@ -1003,6 +1003,11 @@
           <t>Protocol</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Protocol identifier from study_config.yaml and SDTM study domain records.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1041,6 +1046,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SDTM.DM.USUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1079,6 +1089,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SDTM.DM.SUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1132,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>SDTM.DM.SITEID.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1155,6 +1175,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SDTM.DM.AGE.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1198,6 +1223,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Derived age group from SDTM.DM.AGE and protocol age group definitions.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1236,6 +1266,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Numeric age group from AGEGR1.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1274,6 +1309,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>SDTM.DM.RACE.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1312,6 +1352,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SDTM.DM.ETHNIC.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1355,6 +1400,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SDTM.DM.SEX.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1398,6 +1448,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Randomized/planned treatment assignment from SDTM.DM.ARM and study_config.yaml treatment map.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1441,6 +1496,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Numeric planned treatment assignment from study_config.yaml treatment map.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1484,6 +1544,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Actual treatment assignment from first non-missing SDTM.EX exposure record and study_config.yaml treatment map.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1527,6 +1592,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Numeric actual treatment assignment from first non-missing SDTM.EX exposure record and study_config.yaml treatment map.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1565,6 +1635,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Randomization date from SDTM.DM.RFSTDTC or randomization source record.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1608,6 +1683,11 @@
           <t>MT.TRTSDT</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>First exposure start date from SDTM.EX.EXSTDTC.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1651,6 +1731,11 @@
           <t>MT.TRTEDT</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Last exposure end date from SDTM.EX.EXENDTC.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1694,6 +1779,11 @@
           <t>MT.TRTDURD</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Derived from ADSL.TRTSDT and ADSL.TRTEDT.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1742,6 +1832,11 @@
           <t>MT.ITTFL</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Population flag from randomized subject records and protocol population rules.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1790,6 +1885,11 @@
           <t>MT.SAFFL</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Population flag from treated subject records using SDTM.EX exposure evidence.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1833,6 +1933,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Protocol/per-protocol eligibility source records and protocol deviation review.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1876,6 +1981,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Death flag from SDTM.DM.DTHFL and disposition/death records.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1914,6 +2024,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>MT.DTHDT</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Death date from SDTM.DM.DTHDTC or disposition/death records.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1952,6 +2072,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Death cause from disposition/death source records.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1990,6 +2115,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>MT.LSTALVDT</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Last known alive date from maximum non-death contact/assessment date across SDTM source domains.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2033,6 +2168,11 @@
           <t>MT.ECOGBL</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Baseline ECOG from SDTM.QS/VS assessment source before treatment start.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2081,6 +2221,11 @@
           <t>MT.MEASDISF</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Measurable disease flag from baseline tumor/response source assessments.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2124,6 +2269,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Visceral disease flag from baseline lesion source assessments.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2172,6 +2322,11 @@
           <t>MT.PAINBL</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Baseline pain score from pain assessment source before treatment start.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2210,6 +2365,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Baseline PSA from SDTM.LB prostate-specific antigen records.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2248,6 +2408,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Baseline alkaline phosphatase from SDTM.LB records.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2286,6 +2451,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Baseline albumin from SDTM.LB records.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2324,6 +2494,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Baseline lactate dehydrogenase from SDTM.LB records.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2362,6 +2537,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Baseline hemoglobin from SDTM.LB records.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2400,6 +2580,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Investigator-assessed progression source records.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2443,6 +2628,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Investigator-assessed response source records.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2486,6 +2676,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>MT.ECOGBLIF</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Imputation flag derived from ECOGBL source availability and baseline window rules.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2529,6 +2729,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>MT.PSABLIF</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Imputation flag derived from PSABL source availability and baseline window rules.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2572,6 +2782,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>MT.ALPBLIF</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Imputation flag derived from ALPBL source availability and baseline window rules.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2615,6 +2835,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>MT.HGBBLIF</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Imputation flag derived from HGBBL source availability and baseline window rules.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2658,6 +2888,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>MT.ALBBLIF</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Imputation flag derived from ALBBL source availability and baseline window rules.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2701,6 +2941,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>MT.LDHBLIF</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Imputation flag derived from LDHBL source availability and baseline window rules.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2739,6 +2989,11 @@
           <t>Protocol</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Protocol identifier from study_config.yaml and SDTM study domain records.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2777,6 +3032,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>SDTM.DM.USUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2815,6 +3075,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>SDTM.DM.SUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2858,6 +3123,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Randomized/planned treatment assignment from SDTM.DM.ARM and study_config.yaml treatment map.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2901,6 +3171,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Numeric planned treatment assignment from study_config.yaml treatment map.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2939,6 +3214,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Treatment start date inherited from ADSL.TRTSDT unless defined directly for ADSL.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2982,6 +3262,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Analysis parameter code from dataset-specific parameter derivation and source test/category.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3020,6 +3305,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Analysis parameter label from dataset-specific parameter derivation and source test/category.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3058,6 +3348,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Analysis parameter category from dataset-specific parameter map.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3096,6 +3391,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>MT.ADEX_AVAL</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Numeric exposure analysis value from SDTM.EX dose/duration fields by PARAMCD.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3134,6 +3439,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>MT.ADEX_AVALC</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Character exposure analysis value from SDTM.EX dose/duration fields by PARAMCD.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3172,6 +3487,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Analysis visit derived from source visit/date and dataset-specific visit window rules.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3210,6 +3530,11 @@
           <t>Protocol</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Protocol identifier from study_config.yaml and SDTM study domain records.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3248,6 +3573,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>SDTM.DM.USUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3286,6 +3616,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>SDTM.CM plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3324,6 +3659,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>SDTM.CM plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3362,6 +3702,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>SDTM.CM plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3397,7 +3742,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>MT.ADCM_ASTDT</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Analysis start date derived from source start date.</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3790,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>MT.ADCM_AENDT</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Analysis end date derived from source end date.</t>
         </is>
       </c>
     </row>
@@ -3476,6 +3841,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>SDTM.CM plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3511,7 +3881,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>MT.ADCM_ASTDY</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Analysis start relative day derived from ASTDT and ADSL.TRTSDT.</t>
         </is>
       </c>
     </row>
@@ -3557,6 +3937,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>SDTM.CM plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3600,6 +3985,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>SDTM.CM plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3643,6 +4033,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>SDTM.CM plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3681,6 +4076,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>SDTM.CM plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3724,6 +4124,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>SDTM.CM plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3767,6 +4172,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>SDTM.CM plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3805,6 +4215,11 @@
           <t>Protocol</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Protocol identifier from study_config.yaml and SDTM study domain records.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3843,6 +4258,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>SDTM.DM.USUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3881,6 +4301,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3919,6 +4344,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3957,6 +4387,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3995,6 +4430,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4033,6 +4473,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>MT.ADAE_ATOXGR</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Numeric toxicity grade derived from SDTM.AE toxicity grade/severity source fields.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4076,6 +4526,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4114,6 +4569,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4152,6 +4612,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Analysis start date derived from source start date.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4190,6 +4655,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Analysis end date derived from source end date.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4228,6 +4698,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Analysis start relative day derived from ASTDT and ADSL.TRTSDT.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4266,6 +4741,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Analysis end relative day derived from AENDT and ADSL.TRTSDT.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4304,6 +4784,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4342,6 +4827,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4380,6 +4870,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4418,6 +4913,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4456,6 +4956,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4494,6 +4999,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4532,6 +5042,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4570,6 +5085,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4608,6 +5128,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4651,6 +5176,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4694,6 +5224,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Treatment-emergent flag derived from ADAE.ASTDT and ADSL.TRTSDT.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4732,6 +5267,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Adverse event duration derived from ADAE.ASTDT and ADAE.AENDT.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4770,6 +5310,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Duration unit assigned by adverse-event derivation rule.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4808,6 +5353,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4851,6 +5401,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Actual treatment assignment inherited from ADSL.TRT01A.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4894,6 +5449,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Numeric actual treatment assignment inherited from ADSL.TRT01AN.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4932,6 +5492,11 @@
           <t>Protocol</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Protocol identifier from study_config.yaml and SDTM study domain records.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4970,6 +5535,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>SDTM.DM.USUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5008,6 +5578,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>SDTM.DM.SUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5051,6 +5626,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Randomized/planned treatment assignment from SDTM.DM.ARM and study_config.yaml treatment map.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5089,6 +5669,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Treatment start date inherited from ADSL.TRTSDT unless defined directly for ADSL.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5132,6 +5717,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Analysis parameter code from dataset-specific parameter derivation and source test/category.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5170,6 +5760,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Analysis parameter label from dataset-specific parameter derivation and source test/category.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5208,6 +5803,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Numeric parameter ordering from dataset-specific parameter map.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5246,6 +5846,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Analysis parameter category from dataset-specific parameter map.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5284,6 +5889,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>MT.ADLB_AVAL</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Numeric lab analysis value from SDTM.LB.LBSTRESN.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5322,6 +5937,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>MT.ADLB_AVALC</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Character lab analysis value from SDTM.LB.LBSTRESC.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5360,6 +5985,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>SDTM.LB plus ADSL treatment, baseline, and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5398,6 +6028,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>SDTM.LB plus ADSL treatment, baseline, and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5436,6 +6071,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>SDTM.LB plus ADSL treatment, baseline, and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5474,6 +6114,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Analysis visit derived from source visit/date and dataset-specific visit window rules.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5512,6 +6157,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Numeric analysis visit derived from AVISIT and dataset-specific visit ordering.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5550,6 +6200,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>SDTM.LB plus ADSL treatment, baseline, and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5588,6 +6243,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>MT.ADLB_ATOXGR</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Analysis toxicity grade derived from SDTM.LB result, normal range, and grading rules.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5626,6 +6291,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>MT.ADLB_BASE</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Baseline numeric value selected from pre-treatment ADLB.AVAL records.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5664,6 +6339,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>MT.ADLB_BASEC</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Baseline character value selected from pre-treatment ADLB.AVALC records.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5702,6 +6387,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Baseline toxicity grade selected from pre-treatment records.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5740,6 +6430,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>MT.ADLB_CHG</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Change from baseline derived as ADLB.AVAL minus ADLB.BASE.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5778,6 +6478,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>MT.ADLB_PCHG</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Percent change from baseline derived as ADLB.CHG divided by ADLB.BASE.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5821,6 +6531,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Analysis inclusion flag derived from dataset-specific record-selection rules.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5864,6 +6579,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>MT.ADLB_BASEFL</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Baseline flag derived from pre-treatment record-selection rules.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5902,6 +6627,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>SDTM.LB plus ADSL treatment, baseline, and subject-level attributes.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5940,6 +6670,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>MT.ADLB_ADT</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Analysis date from SDTM.LB.LBDTC.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5978,6 +6718,11 @@
           <t>Protocol</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Protocol identifier from study_config.yaml and SDTM study domain records.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6016,6 +6761,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>SDTM.DM.USUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6054,6 +6804,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>SDTM.DM.SUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6097,6 +6852,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Randomized/planned treatment assignment from SDTM.DM.ARM and study_config.yaml treatment map.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -6135,6 +6895,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Treatment start date inherited from ADSL.TRTSDT unless defined directly for ADSL.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6178,6 +6943,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Analysis parameter code from dataset-specific parameter derivation and source test/category.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6216,6 +6986,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Analysis parameter label from dataset-specific parameter derivation and source test/category.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6254,6 +7029,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>MT.ADRS_AVALC</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Character response result from response source assessments and response derivation rules.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -6292,6 +7077,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Analysis date derived from the source assessment date.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6330,6 +7120,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Analysis relative day derived from ADT and ADSL.TRTSDT.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6368,6 +7163,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Analysis visit derived from source visit/date and dataset-specific visit window rules.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6411,6 +7211,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Analysis inclusion flag derived from dataset-specific record-selection rules.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6449,6 +7254,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>MT.ADRS_AVAL</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Numeric response category from ADRS.AVALC response ordering map.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6487,6 +7302,11 @@
           <t>Protocol</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Protocol identifier from study_config.yaml and SDTM study domain records.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6525,6 +7345,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>SDTM.DM.USUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6563,6 +7388,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>SDTM.DM.SUBJID.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6601,6 +7431,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>SDTM.DM.SITEID.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6644,6 +7479,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Randomized/planned treatment assignment from SDTM.DM.ARM and study_config.yaml treatment map.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6687,6 +7527,11 @@
           <t>Assigned</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Numeric planned treatment assignment from study_config.yaml treatment map.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6730,6 +7575,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>MT.ADTTE_ITTFL</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Inherited from ADSL.ITTFL.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6773,6 +7628,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>MT.ADTTE_SAFFL</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Inherited from ADSL.SAFFL.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6816,6 +7681,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Analysis parameter code from dataset-specific parameter derivation and source test/category.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6854,6 +7724,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Analysis parameter label from dataset-specific parameter derivation and source test/category.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6892,6 +7767,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>MT.ADTTE_PARAMN</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Numeric parameter ordering from ADTTE.PARAMCD.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6930,6 +7815,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>MT.ADTTE_PARCAT1</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Time-to-event category from ADTTE.PARAMCD.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -6968,6 +7863,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>ADSL subject-level attributes plus SDTM.DS, SDTM.RS/LS, SDTM.AE, and death/progression source dates by PARAMCD.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -7006,6 +7906,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Analysis date derived from the source assessment date.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7054,6 +7959,11 @@
           <t>MT.CNSR_TTE</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Censoring indicator derived from event/censor source dates by ADTTE.PARAMCD.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -7092,6 +8002,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>ADSL subject-level attributes plus SDTM.DS, SDTM.RS/LS, SDTM.AE, and death/progression source dates by PARAMCD.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -7130,6 +8045,11 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>ADSL subject-level attributes plus SDTM.DS, SDTM.RS/LS, SDTM.AE, and death/progression source dates by PARAMCD.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -7173,6 +8093,11 @@
           <t>MT.AVAL_TTE</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Time-to-event duration derived from ADTTE.STARTDT, ADTTE.ADT, and ADTTE.AVALU.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7211,6 +8136,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>MT.ADTTE_AVALU</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Time-to-event unit assigned by ADTTE parameter derivation.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -7249,6 +8184,16 @@
           <t>Derived</t>
         </is>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>MT.ADEX_PARAMN</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Numeric parameter ordering from ADEX.PARAMCD.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -7285,6 +8230,16 @@
       <c r="K160" t="inlineStr">
         <is>
           <t>Derived</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>MT.ADEX_AVISITN</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Numeric analysis visit derived from ADEX.AVISIT and SDTM.EX sequence/date.</t>
         </is>
       </c>
     </row>
@@ -9944,7 +10899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" customFormat="1" s="1">
@@ -10294,6 +11249,710 @@
       <c r="D15" t="inlineStr">
         <is>
           <t>Censoring indicator, set to 0 if the event occurred, or 1 if censored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MT.DTHDT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Method for DTHDT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Death date derived from SDTM.DM.DTHDTC or disposition/death records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MT.LSTALVDT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Method for LSTALVDT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Last known alive date derived as the maximum non-death contact or assessment date across source domains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MT.ECOGBLIF</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Method for ECOGBLIF</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Baseline ECOG imputation flag derived from ECOGBL source availability and baseline window rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MT.PSABLIF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Method for PSABLIF</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Baseline PSA imputation flag derived from PSABL source availability and baseline window rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MT.ALPBLIF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Method for ALPBLIF</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Baseline alkaline phosphatase imputation flag derived from ALPBL source availability and baseline window rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MT.HGBBLIF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Method for HGBBLIF</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Baseline hemoglobin imputation flag derived from HGBBL source availability and baseline window rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MT.ALBBLIF</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Method for ALBBLIF</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Baseline albumin imputation flag derived from ALBBL source availability and baseline window rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MT.LDHBLIF</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Method for LDHBLIF</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Baseline lactate dehydrogenase imputation flag derived from LDHBL source availability and baseline window rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MT.ADEX_AVAL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Method for ADEX_AVAL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Numeric exposure analysis value derived from SDTM.EX dose, duration, or cycle records according to ADEX.PARAMCD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MT.ADEX_AVALC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Method for ADEX_AVALC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Character exposure analysis value derived from SDTM.EX dose, duration, or cycle records according to ADEX.PARAMCD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MT.ADEX_PARAMN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Method for ADEX_PARAMN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Numeric ADEX parameter ordering derived from ADEX.PARAMCD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MT.ADEX_AVISITN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Method for ADEX_AVISITN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Numeric ADEX analysis visit derived from ADEX.AVISIT and SDTM.EX date or sequence ordering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MT.ADAE_ATOXGR</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Method for ADAE_ATOXGR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Numeric adverse-event toxicity grade derived from SDTM.AE toxicity grade or severity source fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MT.ADLB_AVAL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Method for ADLB_AVAL</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Numeric laboratory analysis value derived from SDTM.LB.LBSTRESN after parameter-specific unit standardization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MT.ADLB_AVALC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Method for ADLB_AVALC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Character laboratory analysis value derived from SDTM.LB.LBSTRESC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MT.ADLB_ATOXGR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Method for ADLB_ATOXGR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Analysis toxicity grade derived from laboratory result, normal range, and grading rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MT.ADLB_BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Method for ADLB_BASE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Baseline numeric value selected from the latest eligible pre-treatment ADLB.AVAL record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MT.ADLB_BASEC</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Method for ADLB_BASEC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Baseline character value selected from the latest eligible pre-treatment ADLB.AVALC record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MT.ADLB_CHG</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Method for ADLB_CHG</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Change from baseline calculated as ADLB.AVAL minus ADLB.BASE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MT.ADLB_PCHG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Method for ADLB_PCHG</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Percent change from baseline calculated as 100 times ADLB.CHG divided by ADLB.BASE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MT.ADLB_BASEFL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Method for ADLB_BASEFL</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Baseline flag set on the selected eligible pre-treatment laboratory record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MT.ADLB_ADT</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Method for ADLB_ADT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Analysis date derived from SDTM.LB.LBDTC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MT.ADRS_AVALC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Method for ADRS_AVALC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Character response result derived from response source assessments and response derivation rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MT.ADRS_AVAL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Method for ADRS_AVAL</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Numeric response category derived from ADRS.AVALC response ordering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MT.ADTTE_ITTFL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Method for ADTTE_ITTFL</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Intent-to-treat flag inherited from ADSL.ITTFL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MT.ADTTE_SAFFL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Method for ADTTE_SAFFL</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Safety population flag inherited from ADSL.SAFFL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MT.ADTTE_PARAMN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Method for ADTTE_PARAMN</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Numeric ADTTE parameter ordering derived from ADTTE.PARAMCD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MT.ADTTE_PARCAT1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Method for ADTTE_PARCAT1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Time-to-event parameter category derived from ADTTE.PARAMCD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MT.ADTTE_AVALU</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Method for ADTTE_AVALU</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Time-to-event unit assigned by ADTTE parameter derivation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MT.ADCM_ASTDT</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Method for ADCM_ASTDT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Analysis medication start date derived from SDTM.CM.CMSTDTC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MT.ADCM_AENDT</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Method for ADCM_AENDT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Analysis medication end date derived from SDTM.CM.CMENDTC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MT.ADCM_ASTDY</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Method for ADCM_ASTDY</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Analysis medication start relative day derived from ADCM.ASTDT and ADSL.TRTSDT.</t>
         </is>
       </c>
     </row>
